--- a/uploads/timetable.xlsx
+++ b/uploads/timetable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4541ce7a804dd02/文档/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{CDAC0DA9-0E48-4459-807D-256DDDC2C14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{170FC92B-8E25-4D7F-8944-8B7B61C419E5}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{CDAC0DA9-0E48-4459-807D-256DDDC2C14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD099159-87D0-4B4F-9CC6-892CE3384F33}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8880" xr2:uid="{3B8B8781-0DA5-460F-AC21-A2D0EB992867}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3B8B8781-0DA5-460F-AC21-A2D0EB992867}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
   <si>
     <t>G.NARAYANAMMA INSTITUTE OF TECHNOLOGY AND SCIENCE</t>
   </si>
@@ -57,9 +57,6 @@
     <t>10:00-11:00</t>
   </si>
   <si>
-    <t>11:00-11:10</t>
-  </si>
-  <si>
     <t>11:10-12:10</t>
   </si>
   <si>
@@ -78,69 +75,24 @@
     <t>Monday</t>
   </si>
   <si>
-    <t>DBMS</t>
-  </si>
-  <si>
-    <t>P&amp;S</t>
-  </si>
-  <si>
-    <t>BREA</t>
-  </si>
-  <si>
-    <t>COI</t>
-  </si>
-  <si>
     <t>LUNCH</t>
   </si>
   <si>
-    <t>DBMS/IT WORKSHOP LAB</t>
-  </si>
-  <si>
     <t>Tuesday</t>
   </si>
   <si>
-    <t>DLD</t>
-  </si>
-  <si>
-    <t>DAA</t>
-  </si>
-  <si>
-    <t>SPORTS</t>
-  </si>
-  <si>
     <t>Wednesday</t>
   </si>
   <si>
-    <t>PP LAB</t>
-  </si>
-  <si>
-    <t>PP</t>
-  </si>
-  <si>
     <t>Thursday</t>
   </si>
   <si>
-    <t>LIBRARY</t>
-  </si>
-  <si>
-    <t>PRE-PLACEMENT TRAINING</t>
-  </si>
-  <si>
     <t>Friday</t>
   </si>
   <si>
-    <t>DBMS(T)</t>
-  </si>
-  <si>
     <t>Saturday</t>
   </si>
   <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>MBC</t>
-  </si>
-  <si>
     <t>Name of the Subject</t>
   </si>
   <si>
@@ -150,73 +102,103 @@
     <t>Name of the Lab</t>
   </si>
   <si>
-    <t xml:space="preserve">Probablity and Statistics(123AU) </t>
-  </si>
-  <si>
-    <t>Dr.R.Lakshmi</t>
-  </si>
-  <si>
-    <t>DataBase Management and System Lab
-(12313)</t>
-  </si>
-  <si>
-    <t>Mrs.B.Spandhana/Mrs.G.Amulya</t>
-  </si>
-  <si>
-    <t>Design and Analysis of Algorithm
- (123AN)</t>
-  </si>
-  <si>
-    <t>Mrs.S.Sandhya</t>
-  </si>
-  <si>
-    <t>Python Programming Lab(12317)</t>
-  </si>
-  <si>
-    <t>Mrs.J.Srilatha / Mrs.Nanda Devi / Mr.B.Syam Sundar Reddy</t>
-  </si>
-  <si>
-    <t>Mrs.B.Spandhana</t>
-  </si>
-  <si>
-    <t>Mr.B.Syam Sundar Reddy /   Mr.M.Kiran</t>
-  </si>
-  <si>
-    <t>Digital Logic Design(123AP)</t>
-  </si>
-  <si>
-    <t>Mrs.Ch.Radhika</t>
-  </si>
-  <si>
     <t>Mathematics Bridge Course</t>
   </si>
   <si>
     <t>Mr.D.Swamy</t>
   </si>
   <si>
-    <t>Python Programming(123AV)</t>
-  </si>
-  <si>
-    <t>Mrs.J.Srilatha</t>
-  </si>
-  <si>
-    <t>Class Teacher  : Mrs.B.Spandhana</t>
-  </si>
-  <si>
-    <t>Dr.T.Anuradha</t>
-  </si>
-  <si>
-    <t>Data Base Mangement and System
-(123AM)</t>
-  </si>
-  <si>
-    <t>Constitution Of India(12312)</t>
-  </si>
-  <si>
-    <t>IT WORKSHOP/DBMS LAB</t>
-  </si>
-  <si>
-    <t>IT Work Shop Lab(12316)</t>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>OOPJ</t>
+  </si>
+  <si>
+    <t>HVPE</t>
+  </si>
+  <si>
+    <t>OOPJ Lab/OSMP LAB</t>
+  </si>
+  <si>
+    <t>Placement Training</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>MP-1</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>OSMP Lab/OOPJ Lab</t>
+  </si>
+  <si>
+    <t>Library/Sports</t>
+  </si>
+  <si>
+    <t>Department Activities</t>
+  </si>
+  <si>
+    <t>Discrete Mathematics</t>
+  </si>
+  <si>
+    <t>Mrs.R.Pallavi</t>
+  </si>
+  <si>
+    <t>Dr.T.Divya Kumari</t>
+  </si>
+  <si>
+    <t>Mr.Ch.Sudharshan Reddy</t>
+  </si>
+  <si>
+    <t>Mrs.Subha Lakshmi</t>
+  </si>
+  <si>
+    <t>Mrs.Durga Bhavani</t>
+  </si>
+  <si>
+    <t>Operating Systems</t>
+  </si>
+  <si>
+    <t>Computer Organization and Architecture</t>
+  </si>
+  <si>
+    <t>Software Engineering</t>
+  </si>
+  <si>
+    <t>Human Values and Professional Ethics</t>
+  </si>
+  <si>
+    <t>Operating Systems and Micro Processor Lab</t>
+  </si>
+  <si>
+    <t>Mini Project-1</t>
+  </si>
+  <si>
+    <t>Dr.T.Divya Kumari/Mrs.Ch.Radhika</t>
+  </si>
+  <si>
+    <t>Mrs.R.Mamatha/Mr.Ch.Sudharshan Reddy</t>
+  </si>
+  <si>
+    <t>Dr.T.Divya Kumari/Mrs.V.Subha Lakshmi</t>
+  </si>
+  <si>
+    <t>Class Teacher  : Dr.T.Divya Kumari</t>
+  </si>
+  <si>
+    <t>Mrs.R.Mamatha</t>
+  </si>
+  <si>
+    <t>Object Oriented  Programming through Java</t>
+  </si>
+  <si>
+    <t>Object Oriented through Programming through Java Lab</t>
   </si>
 </sst>
 </file>
@@ -268,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -291,11 +273,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -306,12 +362,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -324,11 +387,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -660,56 +738,56 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -736,302 +814,281 @@
       <c r="H5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
+      <c r="F6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="B7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="G8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>28</v>
+      <c r="H10" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="19"/>
+      <c r="F11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="20"/>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="3" t="s">
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="14" t="s">
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="13" t="s">
+      <c r="E18" s="21"/>
+      <c r="F18" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-    </row>
-    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-    </row>
-    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-    </row>
-    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-    </row>
-    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="40">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:I19"/>
@@ -1060,16 +1117,18 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="J14:L14"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="F6:F11"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E6:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/uploads/timetable.xlsx
+++ b/uploads/timetable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4541ce7a804dd02/文档/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{CDAC0DA9-0E48-4459-807D-256DDDC2C14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD099159-87D0-4B4F-9CC6-892CE3384F33}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="8_{CDAC0DA9-0E48-4459-807D-256DDDC2C14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A379E091-16B6-4B1C-AA8F-94C2C4C01CF0}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3B8B8781-0DA5-460F-AC21-A2D0EB992867}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8880" xr2:uid="{3B8B8781-0DA5-460F-AC21-A2D0EB992867}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -372,6 +372,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -407,18 +419,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -734,60 +734,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AA8DBB-80B6-4488-99CA-89AB28E9D94C}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -828,30 +828,30 @@
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="14" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -866,14 +866,14 @@
       <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="18"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="16"/>
+      <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -888,25 +888,25 @@
       <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="18"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="22"/>
       <c r="F10" s="6" t="s">
         <v>32</v>
       </c>
@@ -930,193 +930,193 @@
       <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="19"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="8"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="20"/>
-      <c r="L13" s="4"/>
+      <c r="A13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
     </row>
     <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="A14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
     </row>
     <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="A15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
     </row>
     <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="A16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
     </row>
     <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
+      <c r="A17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
     </row>
     <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-    </row>
-    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A18" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="J16:L16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:I17"/>
     <mergeCell ref="J17:L17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="J14:L14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F15:I15"/>
     <mergeCell ref="J15:L15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="J12:K12"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J13:L13"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>

--- a/uploads/timetable.xlsx
+++ b/uploads/timetable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4541ce7a804dd02/文档/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="8_{CDAC0DA9-0E48-4459-807D-256DDDC2C14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A379E091-16B6-4B1C-AA8F-94C2C4C01CF0}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{CDAC0DA9-0E48-4459-807D-256DDDC2C14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{516C834A-77E5-4D12-B44A-47899C31891A}"/>
   <bookViews>
-    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8880" xr2:uid="{3B8B8781-0DA5-460F-AC21-A2D0EB992867}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3B8B8781-0DA5-460F-AC21-A2D0EB992867}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -372,53 +372,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -738,56 +738,56 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -828,30 +828,30 @@
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="18" t="s">
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -866,14 +866,14 @@
       <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="22"/>
+      <c r="E8" s="18"/>
       <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="20"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -888,25 +888,25 @@
       <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="20"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="22"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="18"/>
       <c r="F10" s="6" t="s">
         <v>32</v>
       </c>
@@ -930,162 +930,162 @@
       <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10" t="s">
+      <c r="E12" s="20"/>
+      <c r="F12" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10" t="s">
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="10"/>
+      <c r="K12" s="20"/>
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8" t="s">
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="21"/>
+      <c r="F13" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="8" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="s">
+      <c r="E14" s="21"/>
+      <c r="F14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="9" t="s">
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8" t="s">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
+      <c r="E15" s="21"/>
+      <c r="F15" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="9" t="s">
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8" t="s">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
+      <c r="E16" s="21"/>
+      <c r="F16" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9" t="s">
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8" t="s">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="11" t="s">
+      <c r="E17" s="21"/>
+      <c r="F17" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8" t="s">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="40">
